--- a/config/products.xlsx
+++ b/config/products.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -485,6 +485,364 @@
           <t>cierre_crop_name</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="b">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>aguacate</t>
+        </is>
+      </c>
+      <c r="C2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>aguacate</t>
+        </is>
+      </c>
+      <c r="E2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>133</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Aguacate</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="b">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>tomate</t>
+        </is>
+      </c>
+      <c r="C3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>jitomate|tomate</t>
+        </is>
+      </c>
+      <c r="E3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J3" t="b">
+        <v>0</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>elote</t>
+        </is>
+      </c>
+      <c r="C4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>elote por pieza|elote</t>
+        </is>
+      </c>
+      <c r="E4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J4" t="b">
+        <v>0</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="b">
+        <v>1</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>zanahoria</t>
+        </is>
+      </c>
+      <c r="C5" t="b">
+        <v>1</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>zanahoria</t>
+        </is>
+      </c>
+      <c r="E5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="b">
+        <v>1</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>cebolla</t>
+        </is>
+      </c>
+      <c r="C6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>cebolla</t>
+        </is>
+      </c>
+      <c r="E6" t="b">
+        <v>0</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="b">
+        <v>1</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>chile_jalapeno</t>
+        </is>
+      </c>
+      <c r="C7" t="b">
+        <v>1</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>chile jalapeno por kilo|chile jalapeno|jalapeno</t>
+        </is>
+      </c>
+      <c r="E7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" t="b">
+        <v>0</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="b">
+        <v>1</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>limon</t>
+        </is>
+      </c>
+      <c r="C8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>limon</t>
+        </is>
+      </c>
+      <c r="E8" t="b">
+        <v>0</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" t="b">
+        <v>0</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="b">
+        <v>1</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>platano</t>
+        </is>
+      </c>
+      <c r="C9" t="b">
+        <v>1</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>platano</t>
+        </is>
+      </c>
+      <c r="E9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2</v>
+      </c>
+      <c r="J9" t="b">
+        <v>0</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="b">
+        <v>1</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>mango</t>
+        </is>
+      </c>
+      <c r="C10" t="b">
+        <v>1</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>mango</t>
+        </is>
+      </c>
+      <c r="E10" t="b">
+        <v>0</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2</v>
+      </c>
+      <c r="J10" t="b">
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="b">
+        <v>1</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>papa</t>
+        </is>
+      </c>
+      <c r="C11" t="b">
+        <v>1</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>papa</t>
+        </is>
+      </c>
+      <c r="E11" t="b">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>233</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2</v>
+      </c>
+      <c r="J11" t="b">
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/products.xlsx
+++ b/config/products.xlsx
@@ -539,7 +539,7 @@
         <v>11</v>
       </c>
       <c r="C2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" t="s">
         <v>11</v>
@@ -574,7 +574,7 @@
         <v>13</v>
       </c>
       <c r="C3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" t="s">
         <v>14</v>
@@ -606,7 +606,7 @@
         <v>15</v>
       </c>
       <c r="C4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" t="s">
         <v>16</v>
@@ -638,7 +638,7 @@
         <v>17</v>
       </c>
       <c r="C5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" t="s">
         <v>17</v>
@@ -670,7 +670,7 @@
         <v>18</v>
       </c>
       <c r="C6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" t="s">
         <v>18</v>
@@ -702,7 +702,7 @@
         <v>19</v>
       </c>
       <c r="C7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" t="s">
         <v>20</v>
@@ -734,7 +734,7 @@
         <v>21</v>
       </c>
       <c r="C8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" t="s">
         <v>21</v>
@@ -766,7 +766,7 @@
         <v>22</v>
       </c>
       <c r="C9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" t="s">
         <v>22</v>
@@ -798,7 +798,7 @@
         <v>23</v>
       </c>
       <c r="C10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" t="s">
         <v>23</v>
@@ -830,7 +830,7 @@
         <v>24</v>
       </c>
       <c r="C11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" t="s">
         <v>24</v>

--- a/config/products.xlsx
+++ b/config/products.xlsx
@@ -1,159 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell-G3\Documents\Jupyter-projects\Others\agro-precios\config\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="11664"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="products" sheetId="1" r:id="rId1"/>
-    <sheet name="instructions" sheetId="2" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="productos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="instrucciones" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="37">
-  <si>
-    <t>active</t>
-  </si>
-  <si>
-    <t>canonical_product</t>
-  </si>
-  <si>
-    <t>walmart_enabled</t>
-  </si>
-  <si>
-    <t>walmart_search_terms</t>
-  </si>
-  <si>
-    <t>sniim_enabled</t>
-  </si>
-  <si>
-    <t>sniim_producto_id</t>
-  </si>
-  <si>
-    <t>sniim_origen_id</t>
-  </si>
-  <si>
-    <t>sniim_destino_id</t>
-  </si>
-  <si>
-    <t>sniim_precios_por_id</t>
-  </si>
-  <si>
-    <t>cierre_enabled</t>
-  </si>
-  <si>
-    <t>cierre_crop_name</t>
-  </si>
-  <si>
-    <t>aguacate</t>
-  </si>
-  <si>
-    <t>Aguacate</t>
-  </si>
-  <si>
-    <t>tomate</t>
-  </si>
-  <si>
-    <t>jitomate|tomate</t>
-  </si>
-  <si>
-    <t>elote</t>
-  </si>
-  <si>
-    <t>elote por pieza|elote</t>
-  </si>
-  <si>
-    <t>zanahoria</t>
-  </si>
-  <si>
-    <t>cebolla</t>
-  </si>
-  <si>
-    <t>chile_jalapeno</t>
-  </si>
-  <si>
-    <t>chile jalapeno por kilo|chile jalapeno|jalapeno</t>
-  </si>
-  <si>
-    <t>limon</t>
-  </si>
-  <si>
-    <t>platano</t>
-  </si>
-  <si>
-    <t>mango</t>
-  </si>
-  <si>
-    <t>papa</t>
-  </si>
-  <si>
-    <t>field</t>
-  </si>
-  <si>
-    <t>description</t>
-  </si>
-  <si>
-    <t>TRUE/FALSE. Only active rows are processed.</t>
-  </si>
-  <si>
-    <t>Internal canonical product name used across outputs.</t>
-  </si>
-  <si>
-    <t>TRUE/FALSE to enable Walmart scraping for the row.</t>
-  </si>
-  <si>
-    <t>Pipe-separated Walmart search terms, e.g. jitomate|tomate. Blank falls back to canonical_product.</t>
-  </si>
-  <si>
-    <t>TRUE/FALSE to enable SNIIM scraping for the row.</t>
-  </si>
-  <si>
-    <t>Required SNIIM product id when SNIIM is enabled.</t>
-  </si>
-  <si>
-    <t>Optional. Defaults to -1 when blank.</t>
-  </si>
-  <si>
-    <t>Optional. Defaults to 2 when blank.</t>
-  </si>
-  <si>
-    <t>TRUE/FALSE to enable Cierre Agricola scraping for the row.</t>
-  </si>
-  <si>
-    <t>Required crop label exactly as used by the Cierre Agricola site when enabled.</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -168,43 +47,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -492,367 +421,444 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:K11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>producto_canonico</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>walmart_habilitado</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>terminos_busqueda_walmart</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>sniim_habilitado</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sniim_id_producto</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>sniim_id_origen</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>sniim_id_destino</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>sniim_id_precios_por</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>cierre_agricola_habilitado</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>cultivo_cierre_agricola</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" t="b">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>11</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>aguacate</t>
+        </is>
       </c>
       <c r="C2" t="b">
         <v>1</v>
       </c>
-      <c r="D2" t="s">
-        <v>11</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>aguacate</t>
+        </is>
       </c>
       <c r="E2" t="b">
         <v>1</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="n">
         <v>133</v>
       </c>
-      <c r="G2">
-        <v>-1</v>
-      </c>
-      <c r="H2">
-        <v>-1</v>
-      </c>
-      <c r="I2">
+      <c r="G2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I2" t="n">
         <v>2</v>
       </c>
       <c r="J2" t="b">
         <v>0</v>
       </c>
-      <c r="K2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Aguacate</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" t="b">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
-        <v>13</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>tomate</t>
+        </is>
       </c>
       <c r="C3" t="b">
         <v>1</v>
       </c>
-      <c r="D3" t="s">
-        <v>14</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>jitomate|tomate</t>
+        </is>
       </c>
       <c r="E3" t="b">
         <v>1</v>
       </c>
-      <c r="F3">
+      <c r="F3" t="n">
         <v>836</v>
       </c>
-      <c r="G3">
-        <v>-1</v>
-      </c>
-      <c r="H3">
-        <v>-1</v>
-      </c>
-      <c r="I3">
+      <c r="G3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I3" t="n">
         <v>2</v>
       </c>
       <c r="J3" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K3" t="inlineStr"/>
+    </row>
+    <row r="4">
       <c r="A4" t="b">
         <v>1</v>
       </c>
-      <c r="B4" t="s">
-        <v>15</v>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>elote</t>
+        </is>
       </c>
       <c r="C4" t="b">
         <v>1</v>
       </c>
-      <c r="D4" t="s">
-        <v>16</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>elote por pieza|elote</t>
+        </is>
       </c>
       <c r="E4" t="b">
         <v>1</v>
       </c>
-      <c r="F4">
+      <c r="F4" t="n">
         <v>308</v>
       </c>
-      <c r="G4">
-        <v>-1</v>
-      </c>
-      <c r="H4">
-        <v>-1</v>
-      </c>
-      <c r="I4">
+      <c r="G4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I4" t="n">
         <v>2</v>
       </c>
       <c r="J4" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K4" t="inlineStr"/>
+    </row>
+    <row r="5">
       <c r="A5" t="b">
         <v>1</v>
       </c>
-      <c r="B5" t="s">
-        <v>17</v>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>zanahoria</t>
+        </is>
       </c>
       <c r="C5" t="b">
         <v>1</v>
       </c>
-      <c r="D5" t="s">
-        <v>17</v>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>zanahoria</t>
+        </is>
       </c>
       <c r="E5" t="b">
         <v>1</v>
       </c>
-      <c r="F5">
+      <c r="F5" t="n">
         <v>880</v>
       </c>
-      <c r="G5">
-        <v>-1</v>
-      </c>
-      <c r="H5">
-        <v>-1</v>
-      </c>
-      <c r="I5">
+      <c r="G5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I5" t="n">
         <v>2</v>
       </c>
       <c r="J5" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K5" t="inlineStr"/>
+    </row>
+    <row r="6">
       <c r="A6" t="b">
         <v>1</v>
       </c>
-      <c r="B6" t="s">
-        <v>18</v>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>cebolla</t>
+        </is>
       </c>
       <c r="C6" t="b">
         <v>1</v>
       </c>
-      <c r="D6" t="s">
-        <v>18</v>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>cebolla</t>
+        </is>
       </c>
       <c r="E6" t="b">
         <v>1</v>
       </c>
-      <c r="F6">
+      <c r="F6" t="n">
         <v>183</v>
       </c>
-      <c r="G6">
-        <v>-1</v>
-      </c>
-      <c r="H6">
-        <v>-1</v>
-      </c>
-      <c r="I6">
+      <c r="G6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I6" t="n">
         <v>2</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K6" t="inlineStr"/>
+    </row>
+    <row r="7">
       <c r="A7" t="b">
         <v>1</v>
       </c>
-      <c r="B7" t="s">
-        <v>19</v>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>chile_jalapeno</t>
+        </is>
       </c>
       <c r="C7" t="b">
         <v>1</v>
       </c>
-      <c r="D7" t="s">
-        <v>20</v>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>chile jalapeno por kilo|chile jalapeno|jalapeno</t>
+        </is>
       </c>
       <c r="E7" t="b">
         <v>1</v>
       </c>
-      <c r="F7">
+      <c r="F7" t="n">
         <v>233</v>
       </c>
-      <c r="G7">
-        <v>-1</v>
-      </c>
-      <c r="H7">
-        <v>-1</v>
-      </c>
-      <c r="I7">
+      <c r="G7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I7" t="n">
         <v>2</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K7" t="inlineStr"/>
+    </row>
+    <row r="8">
       <c r="A8" t="b">
         <v>1</v>
       </c>
-      <c r="B8" t="s">
-        <v>21</v>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>limon</t>
+        </is>
       </c>
       <c r="C8" t="b">
         <v>1</v>
       </c>
-      <c r="D8" t="s">
-        <v>21</v>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>limon</t>
+        </is>
       </c>
       <c r="E8" t="b">
         <v>1</v>
       </c>
-      <c r="F8">
+      <c r="F8" t="n">
         <v>421</v>
       </c>
-      <c r="G8">
-        <v>-1</v>
-      </c>
-      <c r="H8">
-        <v>-1</v>
-      </c>
-      <c r="I8">
+      <c r="G8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I8" t="n">
         <v>2</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K8" t="inlineStr"/>
+    </row>
+    <row r="9">
       <c r="A9" t="b">
         <v>1</v>
       </c>
-      <c r="B9" t="s">
-        <v>22</v>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>platano</t>
+        </is>
       </c>
       <c r="C9" t="b">
         <v>1</v>
       </c>
-      <c r="D9" t="s">
-        <v>22</v>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>platano</t>
+        </is>
       </c>
       <c r="E9" t="b">
         <v>1</v>
       </c>
-      <c r="F9">
+      <c r="F9" t="n">
         <v>732</v>
       </c>
-      <c r="G9">
-        <v>-1</v>
-      </c>
-      <c r="H9">
-        <v>-1</v>
-      </c>
-      <c r="I9">
+      <c r="G9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I9" t="n">
         <v>2</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K9" t="inlineStr"/>
+    </row>
+    <row r="10">
       <c r="A10" t="b">
         <v>1</v>
       </c>
-      <c r="B10" t="s">
-        <v>23</v>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>mango</t>
+        </is>
       </c>
       <c r="C10" t="b">
         <v>1</v>
       </c>
-      <c r="D10" t="s">
-        <v>23</v>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>mango</t>
+        </is>
       </c>
       <c r="E10" t="b">
         <v>1</v>
       </c>
-      <c r="F10">
+      <c r="F10" t="n">
         <v>465</v>
       </c>
-      <c r="G10">
-        <v>-1</v>
-      </c>
-      <c r="H10">
-        <v>-1</v>
-      </c>
-      <c r="I10">
+      <c r="G10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I10" t="n">
         <v>2</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K10" t="inlineStr"/>
+    </row>
+    <row r="11">
       <c r="A11" t="b">
         <v>1</v>
       </c>
-      <c r="B11" t="s">
-        <v>24</v>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>papa</t>
+        </is>
       </c>
       <c r="C11" t="b">
         <v>1</v>
       </c>
-      <c r="D11" t="s">
-        <v>24</v>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>papa</t>
+        </is>
       </c>
       <c r="E11" t="b">
         <v>1</v>
       </c>
-      <c r="F11">
+      <c r="F11" t="n">
         <v>740</v>
       </c>
-      <c r="G11">
-        <v>-1</v>
-      </c>
-      <c r="H11">
-        <v>-1</v>
-      </c>
-      <c r="I11">
+      <c r="G11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I11" t="n">
         <v>2</v>
       </c>
       <c r="J11" t="b">
         <v>0</v>
       </c>
+      <c r="K11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -860,104 +866,156 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" t="s">
-        <v>36</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>campo</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>descripcion</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>TRUE/FALSE. Solo se procesan las filas activas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>producto_canonico</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Nombre can?nico interno del producto usado en las salidas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>walmart_habilitado</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>TRUE/FALSE para habilitar el scraping de Walmart en la fila.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>terminos_busqueda_walmart</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>T?rminos de b?squeda de Walmart separados por |, por ejemplo jitomate|tomate. Si est? vac?o, usa producto_canonico.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>sniim_habilitado</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>TRUE/FALSE para habilitar el scraping de SNIIM en la fila.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>sniim_id_producto</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ID de producto SNIIM requerido cuando SNIIM est? habilitado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>sniim_id_origen</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Opcional. Usa -1 por defecto cuando est? vac?o.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>sniim_id_destino</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Opcional. Usa -1 por defecto cuando est? vac?o.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>sniim_id_precios_por</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Opcional. Usa 2 por defecto cuando est? vac?o.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>cierre_agricola_habilitado</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>TRUE/FALSE para habilitar el scraping de Cierre Agr?cola en la fila.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>cultivo_cierre_agricola</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Etiqueta del cultivo exactamente como la usa el sitio de Cierre Agr?cola cuando est? habilitado.</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/config/products.xlsx
+++ b/config/products.xlsx
@@ -426,8 +426,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -452,35 +457,45 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>chedraui_habilitado</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>terminos_busqueda_chedraui</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>sniim_habilitado</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>sniim_id_producto</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>sniim_id_origen</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>sniim_id_destino</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>sniim_id_precios_por</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>cierre_agricola_habilitado</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>cultivo_cierre_agricola</t>
         </is>
@@ -506,22 +521,30 @@
       <c r="E2" t="b">
         <v>1</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>aguacate</t>
+        </is>
+      </c>
+      <c r="G2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
         <v>133</v>
       </c>
-      <c r="G2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-1</v>
-      </c>
       <c r="I2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K2" t="n">
         <v>2</v>
       </c>
-      <c r="J2" t="b">
+      <c r="L2" t="b">
         <v>0</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Aguacate</t>
         </is>
@@ -547,22 +570,29 @@
       <c r="E3" t="b">
         <v>1</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>jitomate|tomate</t>
+        </is>
+      </c>
+      <c r="G3" t="b">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
         <v>836</v>
       </c>
-      <c r="G3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-1</v>
-      </c>
       <c r="I3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K3" t="n">
         <v>2</v>
       </c>
-      <c r="J3" t="b">
+      <c r="L3" t="b">
         <v>0</v>
       </c>
-      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="b">
@@ -584,22 +614,29 @@
       <c r="E4" t="b">
         <v>1</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>elote por pieza|elote</t>
+        </is>
+      </c>
+      <c r="G4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
         <v>308</v>
       </c>
-      <c r="G4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-1</v>
-      </c>
       <c r="I4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K4" t="n">
         <v>2</v>
       </c>
-      <c r="J4" t="b">
+      <c r="L4" t="b">
         <v>0</v>
       </c>
-      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="b">
@@ -621,22 +658,29 @@
       <c r="E5" t="b">
         <v>1</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>zanahoria</t>
+        </is>
+      </c>
+      <c r="G5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
         <v>880</v>
       </c>
-      <c r="G5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-1</v>
-      </c>
       <c r="I5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K5" t="n">
         <v>2</v>
       </c>
-      <c r="J5" t="b">
+      <c r="L5" t="b">
         <v>0</v>
       </c>
-      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="b">
@@ -658,22 +702,29 @@
       <c r="E6" t="b">
         <v>1</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>cebolla</t>
+        </is>
+      </c>
+      <c r="G6" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
         <v>183</v>
       </c>
-      <c r="G6" t="n">
-        <v>-1</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-1</v>
-      </c>
       <c r="I6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K6" t="n">
         <v>2</v>
       </c>
-      <c r="J6" t="b">
+      <c r="L6" t="b">
         <v>0</v>
       </c>
-      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="b">
@@ -695,22 +746,29 @@
       <c r="E7" t="b">
         <v>1</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>chile jalapeno por kilo|chile jalapeno|jalapeno</t>
+        </is>
+      </c>
+      <c r="G7" t="b">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
         <v>233</v>
       </c>
-      <c r="G7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-1</v>
-      </c>
       <c r="I7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K7" t="n">
         <v>2</v>
       </c>
-      <c r="J7" t="b">
+      <c r="L7" t="b">
         <v>0</v>
       </c>
-      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="b">
@@ -732,22 +790,29 @@
       <c r="E8" t="b">
         <v>1</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>limon</t>
+        </is>
+      </c>
+      <c r="G8" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
         <v>421</v>
       </c>
-      <c r="G8" t="n">
-        <v>-1</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-1</v>
-      </c>
       <c r="I8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K8" t="n">
         <v>2</v>
       </c>
-      <c r="J8" t="b">
+      <c r="L8" t="b">
         <v>0</v>
       </c>
-      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="b">
@@ -769,22 +834,29 @@
       <c r="E9" t="b">
         <v>1</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>platano</t>
+        </is>
+      </c>
+      <c r="G9" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
         <v>732</v>
       </c>
-      <c r="G9" t="n">
-        <v>-1</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-1</v>
-      </c>
       <c r="I9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K9" t="n">
         <v>2</v>
       </c>
-      <c r="J9" t="b">
+      <c r="L9" t="b">
         <v>0</v>
       </c>
-      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="b">
@@ -806,22 +878,29 @@
       <c r="E10" t="b">
         <v>1</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>mango</t>
+        </is>
+      </c>
+      <c r="G10" t="b">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
         <v>465</v>
       </c>
-      <c r="G10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-1</v>
-      </c>
       <c r="I10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K10" t="n">
         <v>2</v>
       </c>
-      <c r="J10" t="b">
+      <c r="L10" t="b">
         <v>0</v>
       </c>
-      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="b">
@@ -843,22 +922,29 @@
       <c r="E11" t="b">
         <v>1</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>papa</t>
+        </is>
+      </c>
+      <c r="G11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
         <v>740</v>
       </c>
-      <c r="G11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-1</v>
-      </c>
       <c r="I11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K11" t="n">
         <v>2</v>
       </c>
-      <c r="J11" t="b">
+      <c r="L11" t="b">
         <v>0</v>
       </c>
-      <c r="K11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -871,7 +957,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -937,82 +1023,106 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>sniim_habilitado</t>
+          <t>chedraui_habilitado</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TRUE/FALSE para habilitar el scraping de SNIIM en la fila.</t>
+          <t>TRUE/FALSE para habilitar el scraping de Chedraui en la fila.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>sniim_id_producto</t>
+          <t>terminos_busqueda_chedraui</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ID de producto SNIIM requerido cuando SNIIM est? habilitado.</t>
+          <t>Terminos de busqueda de Chedraui separados por |, por ejemplo jitomate|tomate. Si esta vacio, usa producto_canonico.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>sniim_id_origen</t>
+          <t>sniim_habilitado</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Opcional. Usa -1 por defecto cuando est? vac?o.</t>
+          <t>TRUE/FALSE para habilitar el scraping de SNIIM en la fila.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>sniim_id_destino</t>
+          <t>sniim_id_producto</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Opcional. Usa -1 por defecto cuando est? vac?o.</t>
+          <t>ID de producto SNIIM requerido cuando SNIIM est? habilitado.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>sniim_id_precios_por</t>
+          <t>sniim_id_origen</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Opcional. Usa 2 por defecto cuando est? vac?o.</t>
+          <t>Opcional. Usa -1 por defecto cuando est? vac?o.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>cierre_agricola_habilitado</t>
+          <t>sniim_id_destino</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TRUE/FALSE para habilitar el scraping de Cierre Agr?cola en la fila.</t>
+          <t>Opcional. Usa -1 por defecto cuando est? vac?o.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>sniim_id_precios_por</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Opcional. Usa 2 por defecto cuando est? vac?o.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>cierre_agricola_habilitado</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>TRUE/FALSE para habilitar el scraping de Cierre Agr?cola en la fila.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>cultivo_cierre_agricola</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Etiqueta del cultivo exactamente como la usa el sitio de Cierre Agr?cola cuando est? habilitado.</t>
         </is>

--- a/config/products.xlsx
+++ b/config/products.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22992" windowHeight="9168"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22990" windowHeight="9170"/>
   </bookViews>
   <sheets>
     <sheet name="productos" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="49">
   <si>
     <t>activo</t>
   </si>
@@ -67,15 +67,9 @@
     <t>Aguacate</t>
   </si>
   <si>
-    <t>tomate</t>
-  </si>
-  <si>
     <t>jitomate|tomate</t>
   </si>
   <si>
-    <t>elote</t>
-  </si>
-  <si>
     <t>elote por pieza|elote</t>
   </si>
   <si>
@@ -85,9 +79,6 @@
     <t>cebolla</t>
   </si>
   <si>
-    <t>chile_jalapeno</t>
-  </si>
-  <si>
     <t>chile jalapeno por kilo|chile jalapeno|jalapeno</t>
   </si>
   <si>
@@ -149,6 +140,33 @@
   </si>
   <si>
     <t>mango ataulfo</t>
+  </si>
+  <si>
+    <t>Limón</t>
+  </si>
+  <si>
+    <t>Plátano</t>
+  </si>
+  <si>
+    <t>Mango</t>
+  </si>
+  <si>
+    <t>Papa</t>
+  </si>
+  <si>
+    <t>Cebolla</t>
+  </si>
+  <si>
+    <t>Zanahoria</t>
+  </si>
+  <si>
+    <t>Elote</t>
+  </si>
+  <si>
+    <t>Tomate rojo</t>
+  </si>
+  <si>
+    <t>Chile verde</t>
   </si>
 </sst>
 </file>
@@ -512,12 +530,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="4" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -558,12 +576,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" t="b">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="b">
         <v>1</v>
@@ -599,24 +617,24 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" t="b">
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
         <v>15</v>
       </c>
-      <c r="C3" t="b">
-        <v>1</v>
-      </c>
-      <c r="D3" t="s">
-        <v>16</v>
-      </c>
       <c r="E3" t="b">
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G3" t="b">
         <v>1</v>
@@ -637,24 +655,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" t="b">
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="C4" t="b">
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E4" t="b">
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G4" t="b">
         <v>1</v>
@@ -675,24 +693,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" t="b">
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="C5" t="b">
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G5" t="b">
         <v>1</v>
@@ -713,24 +731,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" t="b">
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="C6" t="b">
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G6" t="b">
         <v>1</v>
@@ -751,24 +769,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" t="b">
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="C7" t="b">
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E7" t="b">
         <v>1</v>
       </c>
       <c r="F7" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G7" t="b">
         <v>1</v>
@@ -789,24 +807,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" t="b">
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="C8" t="b">
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E8" t="b">
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G8" t="b">
         <v>1</v>
@@ -827,24 +845,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" t="b">
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="C9" t="b">
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E9" t="b">
         <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G9" t="b">
         <v>1</v>
@@ -865,24 +883,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" t="b">
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="C10" t="b">
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E10" t="b">
         <v>1</v>
       </c>
       <c r="F10" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G10" t="b">
         <v>1</v>
@@ -903,24 +921,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" t="b">
         <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="C11" t="b">
         <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E11" t="b">
         <v>1</v>
       </c>
       <c r="F11" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G11" t="b">
         <v>1</v>
@@ -949,118 +967,118 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="1" t="s">
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/config/products.xlsx
+++ b/config/products.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="48">
   <si>
     <t>activo</t>
   </si>
@@ -89,9 +89,6 @@
   </si>
   <si>
     <t>mango</t>
-  </si>
-  <si>
-    <t>papa</t>
   </si>
   <si>
     <t>campo</t>
@@ -622,7 +619,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C3" t="b">
         <v>1</v>
@@ -654,13 +651,16 @@
       <c r="L3" t="b">
         <v>0</v>
       </c>
+      <c r="M3" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" t="b">
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C4" t="b">
         <v>1</v>
@@ -692,13 +692,16 @@
       <c r="L4" t="b">
         <v>0</v>
       </c>
+      <c r="M4" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" t="b">
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C5" t="b">
         <v>1</v>
@@ -730,13 +733,16 @@
       <c r="L5" t="b">
         <v>0</v>
       </c>
+      <c r="M5" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" t="b">
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C6" t="b">
         <v>1</v>
@@ -768,13 +774,16 @@
       <c r="L6" t="b">
         <v>0</v>
       </c>
+      <c r="M6" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" t="b">
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C7" t="b">
         <v>1</v>
@@ -806,13 +815,16 @@
       <c r="L7" t="b">
         <v>0</v>
       </c>
+      <c r="M7" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" t="b">
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C8" t="b">
         <v>1</v>
@@ -844,13 +856,16 @@
       <c r="L8" t="b">
         <v>0</v>
       </c>
+      <c r="M8" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" t="b">
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C9" t="b">
         <v>1</v>
@@ -882,13 +897,16 @@
       <c r="L9" t="b">
         <v>0</v>
       </c>
+      <c r="M9" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" t="b">
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C10" t="b">
         <v>1</v>
@@ -900,7 +918,7 @@
         <v>1</v>
       </c>
       <c r="F10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G10" t="b">
         <v>1</v>
@@ -920,25 +938,28 @@
       <c r="L10" t="b">
         <v>0</v>
       </c>
+      <c r="M10" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" t="b">
         <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C11" t="b">
         <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="E11" t="b">
         <v>1</v>
       </c>
       <c r="F11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G11" t="b">
         <v>1</v>
@@ -957,6 +978,9 @@
       </c>
       <c r="L11" t="b">
         <v>0</v>
+      </c>
+      <c r="M11" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -971,10 +995,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
@@ -982,7 +1006,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -990,7 +1014,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
@@ -998,7 +1022,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
@@ -1006,7 +1030,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
@@ -1014,7 +1038,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
@@ -1022,7 +1046,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
@@ -1030,7 +1054,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
@@ -1038,7 +1062,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
@@ -1046,7 +1070,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
@@ -1054,7 +1078,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
@@ -1062,7 +1086,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
@@ -1070,7 +1094,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
@@ -1078,7 +1102,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/config/products.xlsx
+++ b/config/products.xlsx
@@ -535,8 +535,20 @@
   <dimension ref="A1:O11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="4" max="6" width="13" customWidth="1"/>
-    <col min="15" max="15" width="12.36328125" customWidth="1"/>
+    <col min="2" max="2" width="17.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="40.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="40.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.6328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.90625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.7265625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.7265625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="23.7265625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="20.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.35">
@@ -579,10 +591,10 @@
       <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
     </row>
@@ -627,7 +639,7 @@
         <v>15</v>
       </c>
       <c r="N2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O2" t="s">
         <v>15</v>
@@ -674,7 +686,7 @@
         <v>17</v>
       </c>
       <c r="N3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3" t="s">
         <v>17</v>
@@ -721,7 +733,7 @@
         <v>19</v>
       </c>
       <c r="N4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="s">
         <v>19</v>
@@ -768,7 +780,7 @@
         <v>21</v>
       </c>
       <c r="N5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5" t="s">
         <v>21</v>
@@ -815,7 +827,7 @@
         <v>23</v>
       </c>
       <c r="N6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6" t="s">
         <v>23</v>
@@ -862,7 +874,7 @@
         <v>25</v>
       </c>
       <c r="N7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="s">
         <v>25</v>
@@ -909,7 +921,7 @@
         <v>27</v>
       </c>
       <c r="N8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="s">
         <v>27</v>
@@ -956,7 +968,7 @@
         <v>29</v>
       </c>
       <c r="N9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9" t="s">
         <v>29</v>
@@ -1003,7 +1015,7 @@
         <v>31</v>
       </c>
       <c r="N10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O10" t="s">
         <v>31</v>
@@ -1050,7 +1062,7 @@
         <v>34</v>
       </c>
       <c r="N11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11" t="s">
         <v>34</v>

--- a/config/products.xlsx
+++ b/config/products.xlsx
@@ -1,204 +1,49 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell-G3\Documents\Jupyter-projects\Others\agro-precios\config\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22990" windowHeight="9170"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="22990" windowHeight="9170" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="productos" sheetId="1" r:id="rId1"/>
-    <sheet name="instrucciones" sheetId="2" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="productos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="instrucciones" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="proxies_internacionales" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="50">
-  <si>
-    <t>activo</t>
-  </si>
-  <si>
-    <t>producto_canonico</t>
-  </si>
-  <si>
-    <t>walmart_habilitado</t>
-  </si>
-  <si>
-    <t>terminos_busqueda_walmart</t>
-  </si>
-  <si>
-    <t>chedraui_habilitado</t>
-  </si>
-  <si>
-    <t>terminos_busqueda_chedraui</t>
-  </si>
-  <si>
-    <t>sniim_habilitado</t>
-  </si>
-  <si>
-    <t>sniim_id_producto</t>
-  </si>
-  <si>
-    <t>sniim_id_origen</t>
-  </si>
-  <si>
-    <t>sniim_id_destino</t>
-  </si>
-  <si>
-    <t>sniim_id_precios_por</t>
-  </si>
-  <si>
-    <t>cierre_agricola_habilitado</t>
-  </si>
-  <si>
-    <t>cultivo_cierre_agricola</t>
-  </si>
-  <si>
-    <t>avance_agricola_habilitado</t>
-  </si>
-  <si>
-    <t>cultivo_avance_agricola</t>
-  </si>
-  <si>
-    <t>Aguacate</t>
-  </si>
-  <si>
-    <t>aguacate</t>
-  </si>
-  <si>
-    <t>Tomate rojo</t>
-  </si>
-  <si>
-    <t>jitomate|tomate</t>
-  </si>
-  <si>
-    <t>Elote</t>
-  </si>
-  <si>
-    <t>elote por pieza|elote</t>
-  </si>
-  <si>
-    <t>Zanahoria</t>
-  </si>
-  <si>
-    <t>zanahoria</t>
-  </si>
-  <si>
-    <t>Cebolla</t>
-  </si>
-  <si>
-    <t>cebolla</t>
-  </si>
-  <si>
-    <t>Chile verde</t>
-  </si>
-  <si>
-    <t>chile jalapeno por kilo|chile jalapeno|jalapeno</t>
-  </si>
-  <si>
-    <t>Limón</t>
-  </si>
-  <si>
-    <t>limon</t>
-  </si>
-  <si>
-    <t>Plátano</t>
-  </si>
-  <si>
-    <t>platano</t>
-  </si>
-  <si>
-    <t>Mango</t>
-  </si>
-  <si>
-    <t>mango</t>
-  </si>
-  <si>
-    <t>mango ataulfo</t>
-  </si>
-  <si>
-    <t>Papa</t>
-  </si>
-  <si>
-    <t>papa blanca</t>
-  </si>
-  <si>
-    <t>campo</t>
-  </si>
-  <si>
-    <t>descripcion</t>
-  </si>
-  <si>
-    <t>TRUE/FALSE. Solo se procesan las filas activas.</t>
-  </si>
-  <si>
-    <t>Nombre can?nico interno del producto usado en las salidas.</t>
-  </si>
-  <si>
-    <t>TRUE/FALSE para habilitar el scraping de Walmart en la fila.</t>
-  </si>
-  <si>
-    <t>T?rminos de b?squeda de Walmart separados por |, por ejemplo jitomate|tomate. Si est? vac?o, usa producto_canonico.</t>
-  </si>
-  <si>
-    <t>TRUE/FALSE para habilitar el scraping de Chedraui en la fila.</t>
-  </si>
-  <si>
-    <t>Terminos de busqueda de Chedraui separados por |, por ejemplo jitomate|tomate. Si esta vacio, usa producto_canonico.</t>
-  </si>
-  <si>
-    <t>TRUE/FALSE para habilitar el scraping de SNIIM en la fila.</t>
-  </si>
-  <si>
-    <t>ID de producto SNIIM requerido cuando SNIIM est? habilitado.</t>
-  </si>
-  <si>
-    <t>Opcional. Usa -1 por defecto cuando est? vac?o.</t>
-  </si>
-  <si>
-    <t>Opcional. Usa 2 por defecto cuando est? vac?o.</t>
-  </si>
-  <si>
-    <t>TRUE/FALSE para habilitar el scraping de Cierre Agr?cola en la fila.</t>
-  </si>
-  <si>
-    <t>Etiqueta del cultivo exactamente como la usa el sitio de Cierre Agr?cola cuando est? habilitado.</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="Calibri"/>
+      <b val="1"/>
       <sz val="11"/>
-      <name val="Calibri"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -221,29 +66,97 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -531,541 +444,675 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:O11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="17.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="40.08984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.7265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="40.08984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.6328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.1796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.1796875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.90625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="22.7265625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.7265625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="23.7265625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="20.7265625" bestFit="1" customWidth="1"/>
+    <col width="17.1796875" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="17.453125" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="40.08984375" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="17.7265625" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="40.08984375" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="14.81640625" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col width="16.6328125" bestFit="1" customWidth="1" min="8" max="8"/>
+    <col width="14.1796875" bestFit="1" customWidth="1" min="9" max="9"/>
+    <col width="15.1796875" bestFit="1" customWidth="1" min="10" max="10"/>
+    <col width="18.90625" bestFit="1" customWidth="1" min="11" max="11"/>
+    <col width="22.7265625" bestFit="1" customWidth="1" min="12" max="12"/>
+    <col width="19.7265625" bestFit="1" customWidth="1" min="13" max="13"/>
+    <col width="23.7265625" bestFit="1" customWidth="1" min="14" max="14"/>
+    <col width="20.7265625" bestFit="1" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>producto_canonico</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>walmart_habilitado</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>terminos_busqueda_walmart</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>chedraui_habilitado</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>terminos_busqueda_chedraui</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>sniim_habilitado</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>sniim_id_producto</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>sniim_id_origen</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>sniim_id_destino</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>sniim_id_precios_por</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>cierre_agricola_habilitado</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>cultivo_cierre_agricola</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>avance_agricola_habilitado</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>cultivo_avance_agricola</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" t="b">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>15</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Aguacate</t>
+        </is>
       </c>
       <c r="C2" t="b">
         <v>1</v>
       </c>
-      <c r="D2" t="s">
-        <v>16</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>aguacate</t>
+        </is>
       </c>
       <c r="E2" t="b">
         <v>1</v>
       </c>
-      <c r="F2" t="s">
-        <v>16</v>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>aguacate</t>
+        </is>
       </c>
       <c r="G2" t="b">
         <v>1</v>
       </c>
-      <c r="H2">
+      <c r="H2" t="n">
         <v>133</v>
       </c>
-      <c r="I2">
+      <c r="I2" t="n">
         <v>-1</v>
       </c>
-      <c r="J2">
+      <c r="J2" t="n">
         <v>-1</v>
       </c>
-      <c r="K2">
+      <c r="K2" t="n">
         <v>2</v>
       </c>
       <c r="L2" t="b">
         <v>0</v>
       </c>
-      <c r="M2" t="s">
-        <v>15</v>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Aguacate</t>
+        </is>
       </c>
       <c r="N2" t="b">
         <v>0</v>
       </c>
-      <c r="O2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Aguacate</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" t="b">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
-        <v>17</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Tomate rojo</t>
+        </is>
       </c>
       <c r="C3" t="b">
         <v>1</v>
       </c>
-      <c r="D3" t="s">
-        <v>18</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>jitomate|tomate</t>
+        </is>
       </c>
       <c r="E3" t="b">
         <v>1</v>
       </c>
-      <c r="F3" t="s">
-        <v>18</v>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>jitomate|tomate</t>
+        </is>
       </c>
       <c r="G3" t="b">
         <v>1</v>
       </c>
-      <c r="H3">
+      <c r="H3" t="n">
         <v>836</v>
       </c>
-      <c r="I3">
+      <c r="I3" t="n">
         <v>-1</v>
       </c>
-      <c r="J3">
+      <c r="J3" t="n">
         <v>-1</v>
       </c>
-      <c r="K3">
+      <c r="K3" t="n">
         <v>2</v>
       </c>
       <c r="L3" t="b">
         <v>0</v>
       </c>
-      <c r="M3" t="s">
-        <v>17</v>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Tomate rojo</t>
+        </is>
       </c>
       <c r="N3" t="b">
         <v>0</v>
       </c>
-      <c r="O3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Tomate rojo</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" t="b">
         <v>1</v>
       </c>
-      <c r="B4" t="s">
-        <v>19</v>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Elote</t>
+        </is>
       </c>
       <c r="C4" t="b">
         <v>1</v>
       </c>
-      <c r="D4" t="s">
-        <v>20</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>elote por pieza|elote</t>
+        </is>
       </c>
       <c r="E4" t="b">
         <v>1</v>
       </c>
-      <c r="F4" t="s">
-        <v>20</v>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>elote por pieza|elote</t>
+        </is>
       </c>
       <c r="G4" t="b">
         <v>1</v>
       </c>
-      <c r="H4">
+      <c r="H4" t="n">
         <v>308</v>
       </c>
-      <c r="I4">
+      <c r="I4" t="n">
         <v>-1</v>
       </c>
-      <c r="J4">
+      <c r="J4" t="n">
         <v>-1</v>
       </c>
-      <c r="K4">
+      <c r="K4" t="n">
         <v>2</v>
       </c>
       <c r="L4" t="b">
         <v>0</v>
       </c>
-      <c r="M4" t="s">
-        <v>19</v>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Elote</t>
+        </is>
       </c>
       <c r="N4" t="b">
         <v>0</v>
       </c>
-      <c r="O4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Elote</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" t="b">
         <v>1</v>
       </c>
-      <c r="B5" t="s">
-        <v>21</v>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Zanahoria</t>
+        </is>
       </c>
       <c r="C5" t="b">
         <v>1</v>
       </c>
-      <c r="D5" t="s">
-        <v>22</v>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>zanahoria</t>
+        </is>
       </c>
       <c r="E5" t="b">
         <v>1</v>
       </c>
-      <c r="F5" t="s">
-        <v>22</v>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>zanahoria</t>
+        </is>
       </c>
       <c r="G5" t="b">
         <v>1</v>
       </c>
-      <c r="H5">
+      <c r="H5" t="n">
         <v>880</v>
       </c>
-      <c r="I5">
+      <c r="I5" t="n">
         <v>-1</v>
       </c>
-      <c r="J5">
+      <c r="J5" t="n">
         <v>-1</v>
       </c>
-      <c r="K5">
+      <c r="K5" t="n">
         <v>2</v>
       </c>
       <c r="L5" t="b">
         <v>0</v>
       </c>
-      <c r="M5" t="s">
-        <v>21</v>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Zanahoria</t>
+        </is>
       </c>
       <c r="N5" t="b">
         <v>0</v>
       </c>
-      <c r="O5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Zanahoria</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" t="b">
         <v>1</v>
       </c>
-      <c r="B6" t="s">
-        <v>23</v>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Cebolla</t>
+        </is>
       </c>
       <c r="C6" t="b">
         <v>1</v>
       </c>
-      <c r="D6" t="s">
-        <v>24</v>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>cebolla</t>
+        </is>
       </c>
       <c r="E6" t="b">
         <v>1</v>
       </c>
-      <c r="F6" t="s">
-        <v>24</v>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>cebolla</t>
+        </is>
       </c>
       <c r="G6" t="b">
         <v>1</v>
       </c>
-      <c r="H6">
+      <c r="H6" t="n">
         <v>183</v>
       </c>
-      <c r="I6">
+      <c r="I6" t="n">
         <v>-1</v>
       </c>
-      <c r="J6">
+      <c r="J6" t="n">
         <v>-1</v>
       </c>
-      <c r="K6">
+      <c r="K6" t="n">
         <v>2</v>
       </c>
       <c r="L6" t="b">
         <v>0</v>
       </c>
-      <c r="M6" t="s">
-        <v>23</v>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Cebolla</t>
+        </is>
       </c>
       <c r="N6" t="b">
         <v>0</v>
       </c>
-      <c r="O6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Cebolla</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" t="b">
         <v>1</v>
       </c>
-      <c r="B7" t="s">
-        <v>25</v>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Chile verde</t>
+        </is>
       </c>
       <c r="C7" t="b">
         <v>1</v>
       </c>
-      <c r="D7" t="s">
-        <v>26</v>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>chile jalapeno por kilo|chile jalapeno|jalapeno</t>
+        </is>
       </c>
       <c r="E7" t="b">
         <v>1</v>
       </c>
-      <c r="F7" t="s">
-        <v>26</v>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>chile jalapeno por kilo|chile jalapeno|jalapeno</t>
+        </is>
       </c>
       <c r="G7" t="b">
         <v>1</v>
       </c>
-      <c r="H7">
+      <c r="H7" t="n">
         <v>233</v>
       </c>
-      <c r="I7">
+      <c r="I7" t="n">
         <v>-1</v>
       </c>
-      <c r="J7">
+      <c r="J7" t="n">
         <v>-1</v>
       </c>
-      <c r="K7">
+      <c r="K7" t="n">
         <v>2</v>
       </c>
       <c r="L7" t="b">
         <v>0</v>
       </c>
-      <c r="M7" t="s">
-        <v>25</v>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Chile verde</t>
+        </is>
       </c>
       <c r="N7" t="b">
         <v>0</v>
       </c>
-      <c r="O7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Chile verde</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" t="b">
         <v>1</v>
       </c>
-      <c r="B8" t="s">
-        <v>27</v>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Limón</t>
+        </is>
       </c>
       <c r="C8" t="b">
         <v>1</v>
       </c>
-      <c r="D8" t="s">
-        <v>28</v>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>limon</t>
+        </is>
       </c>
       <c r="E8" t="b">
         <v>1</v>
       </c>
-      <c r="F8" t="s">
-        <v>28</v>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>limon</t>
+        </is>
       </c>
       <c r="G8" t="b">
         <v>1</v>
       </c>
-      <c r="H8">
+      <c r="H8" t="n">
         <v>421</v>
       </c>
-      <c r="I8">
+      <c r="I8" t="n">
         <v>-1</v>
       </c>
-      <c r="J8">
+      <c r="J8" t="n">
         <v>-1</v>
       </c>
-      <c r="K8">
+      <c r="K8" t="n">
         <v>2</v>
       </c>
       <c r="L8" t="b">
         <v>0</v>
       </c>
-      <c r="M8" t="s">
-        <v>27</v>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Limón</t>
+        </is>
       </c>
       <c r="N8" t="b">
         <v>0</v>
       </c>
-      <c r="O8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Limón</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" t="b">
         <v>1</v>
       </c>
-      <c r="B9" t="s">
-        <v>29</v>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Plátano</t>
+        </is>
       </c>
       <c r="C9" t="b">
         <v>1</v>
       </c>
-      <c r="D9" t="s">
-        <v>30</v>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>platano</t>
+        </is>
       </c>
       <c r="E9" t="b">
         <v>1</v>
       </c>
-      <c r="F9" t="s">
-        <v>30</v>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>platano</t>
+        </is>
       </c>
       <c r="G9" t="b">
         <v>1</v>
       </c>
-      <c r="H9">
+      <c r="H9" t="n">
         <v>732</v>
       </c>
-      <c r="I9">
+      <c r="I9" t="n">
         <v>-1</v>
       </c>
-      <c r="J9">
+      <c r="J9" t="n">
         <v>-1</v>
       </c>
-      <c r="K9">
+      <c r="K9" t="n">
         <v>2</v>
       </c>
       <c r="L9" t="b">
         <v>0</v>
       </c>
-      <c r="M9" t="s">
-        <v>29</v>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Plátano</t>
+        </is>
       </c>
       <c r="N9" t="b">
         <v>0</v>
       </c>
-      <c r="O9" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Plátano</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" t="b">
         <v>1</v>
       </c>
-      <c r="B10" t="s">
-        <v>31</v>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
       </c>
       <c r="C10" t="b">
         <v>1</v>
       </c>
-      <c r="D10" t="s">
-        <v>32</v>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>mango</t>
+        </is>
       </c>
       <c r="E10" t="b">
         <v>1</v>
       </c>
-      <c r="F10" t="s">
-        <v>33</v>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>mango ataulfo</t>
+        </is>
       </c>
       <c r="G10" t="b">
         <v>1</v>
       </c>
-      <c r="H10">
+      <c r="H10" t="n">
         <v>465</v>
       </c>
-      <c r="I10">
+      <c r="I10" t="n">
         <v>-1</v>
       </c>
-      <c r="J10">
+      <c r="J10" t="n">
         <v>-1</v>
       </c>
-      <c r="K10">
+      <c r="K10" t="n">
         <v>2</v>
       </c>
       <c r="L10" t="b">
         <v>0</v>
       </c>
-      <c r="M10" t="s">
-        <v>31</v>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
       </c>
       <c r="N10" t="b">
         <v>0</v>
       </c>
-      <c r="O10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11" t="b">
         <v>1</v>
       </c>
-      <c r="B11" t="s">
-        <v>34</v>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Papa</t>
+        </is>
       </c>
       <c r="C11" t="b">
         <v>1</v>
       </c>
-      <c r="D11" t="s">
-        <v>35</v>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>papa blanca</t>
+        </is>
       </c>
       <c r="E11" t="b">
         <v>1</v>
       </c>
-      <c r="F11" t="s">
-        <v>35</v>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>papa blanca</t>
+        </is>
       </c>
       <c r="G11" t="b">
         <v>1</v>
       </c>
-      <c r="H11">
+      <c r="H11" t="n">
         <v>740</v>
       </c>
-      <c r="I11">
+      <c r="I11" t="n">
         <v>-1</v>
       </c>
-      <c r="J11">
+      <c r="J11" t="n">
         <v>-1</v>
       </c>
-      <c r="K11">
+      <c r="K11" t="n">
         <v>2</v>
       </c>
       <c r="L11" t="b">
         <v>0</v>
       </c>
-      <c r="M11" t="s">
-        <v>34</v>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Papa</t>
+        </is>
       </c>
       <c r="N11" t="b">
         <v>0</v>
       </c>
-      <c r="O11" t="s">
-        <v>34</v>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Papa</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1074,120 +1121,1406 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" t="s">
-        <v>49</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>campo</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>descripcion</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>TRUE/FALSE. Solo se procesan las filas activas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>producto_canonico</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Nombre can?nico interno del producto usado en las salidas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>walmart_habilitado</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>TRUE/FALSE para habilitar el scraping de Walmart en la fila.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>terminos_busqueda_walmart</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>T?rminos de b?squeda de Walmart separados por |, por ejemplo jitomate|tomate. Si est? vac?o, usa producto_canonico.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>chedraui_habilitado</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>TRUE/FALSE para habilitar el scraping de Chedraui en la fila.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>terminos_busqueda_chedraui</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Terminos de busqueda de Chedraui separados por |, por ejemplo jitomate|tomate. Si esta vacio, usa producto_canonico.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>sniim_habilitado</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>TRUE/FALSE para habilitar el scraping de SNIIM en la fila.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>sniim_id_producto</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ID de producto SNIIM requerido cuando SNIIM est? habilitado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>sniim_id_origen</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Opcional. Usa -1 por defecto cuando est? vac?o.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>sniim_id_destino</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Opcional. Usa -1 por defecto cuando est? vac?o.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>sniim_id_precios_por</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Opcional. Usa 2 por defecto cuando est? vac?o.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>cierre_agricola_habilitado</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>TRUE/FALSE para habilitar el scraping de Cierre Agr?cola en la fila.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>cultivo_cierre_agricola</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Etiqueta del cultivo exactamente como la usa el sitio de Cierre Agr?cola cuando est? habilitado.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>producto_canonico</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>proxy_id</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>fuente</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>serie</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>tipo_proxy</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>uso_modelo</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>frecuencia</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>moneda</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>unidad_origen</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>nota_metodologica</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="b">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Aguacate</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>usda_ams_aguacate</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>usda_ams</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>avocado</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>fuerte</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>segun_reporte_usda</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Precio de mercado mayorista de EE. UU. desde archivos publicos descargados de USDA AMS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="b">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Tomate rojo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>usda_ams_tomate_rojo</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>usda_ams</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>tomato</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>fuerte</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>segun_reporte_usda</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Precio de mercado mayorista de EE. UU. desde archivos publicos descargados de USDA AMS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Limón</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>usda_ams_limon</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>usda_ams</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>lime</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>fuerte</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>segun_reporte_usda</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Precio de mercado mayorista de EE. UU. desde archivos publicos descargados de USDA AMS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="b">
+        <v>1</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>usda_ams_mango</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>usda_ams</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>mango</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>fuerte</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>segun_reporte_usda</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Precio de mercado mayorista de EE. UU. desde archivos publicos descargados de USDA AMS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="b">
+        <v>1</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Chile verde</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>usda_ams_chile_verde</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>usda_ams</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>pepper</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>segun_reporte_usda</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Precio de mercado mayorista de EE. UU. desde archivos publicos descargados de USDA AMS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="b">
+        <v>1</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Cebolla</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>usda_ams_cebolla</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>usda_ams</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>onion</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>segun_reporte_usda</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Precio de mercado mayorista de EE. UU. desde archivos publicos descargados de USDA AMS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="b">
+        <v>1</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Papa</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>usda_ams_papa</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>usda_ams</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>potato</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>segun_reporte_usda</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Precio de mercado mayorista de EE. UU. desde archivos publicos descargados de USDA AMS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="b">
+        <v>1</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Zanahoria</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>usda_ams_zanahoria</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>usda_ams</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>carrot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>segun_reporte_usda</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Precio de mercado mayorista de EE. UU. desde archivos publicos descargados de USDA AMS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="b">
+        <v>1</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Aguacate</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>fx_usdmxn</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>DEXMXUS</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>fx</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>MXN por USD</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Tipo de cambio spot MXN por USD publicado en FRED; no requiere token.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="b">
+        <v>1</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Tomate rojo</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>fx_usdmxn</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>DEXMXUS</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>fx</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>MXN por USD</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Tipo de cambio spot MXN por USD publicado en FRED; no requiere token.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="b">
+        <v>1</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Limón</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>fx_usdmxn</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>DEXMXUS</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>fx</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>MXN por USD</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Tipo de cambio spot MXN por USD publicado en FRED; no requiere token.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="b">
+        <v>1</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>fx_usdmxn</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>DEXMXUS</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>fx</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>MXN por USD</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Tipo de cambio spot MXN por USD publicado en FRED; no requiere token.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="b">
+        <v>1</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Chile verde</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>fx_usdmxn</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>DEXMXUS</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>fx</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>MXN por USD</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Tipo de cambio spot MXN por USD publicado en FRED; no requiere token.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="b">
+        <v>1</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Cebolla</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>fx_usdmxn</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>DEXMXUS</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>fx</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>MXN por USD</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Tipo de cambio spot MXN por USD publicado en FRED; no requiere token.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="b">
+        <v>1</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Papa</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>fx_usdmxn</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>DEXMXUS</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>fx</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>MXN por USD</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Tipo de cambio spot MXN por USD publicado en FRED; no requiere token.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="b">
+        <v>1</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Zanahoria</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>fx_usdmxn</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>DEXMXUS</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>fx</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>MXN por USD</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Tipo de cambio spot MXN por USD publicado en FRED; no requiere token.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="b">
+        <v>1</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Plátano</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>fx_usdmxn</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>DEXMXUS</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>fx</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>MXN por USD</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Tipo de cambio spot MXN por USD publicado en FRED; no requiere token.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="b">
+        <v>1</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Elote</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>fx_usdmxn</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>DEXMXUS</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>fx</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>MXN por USD</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Tipo de cambio spot MXN por USD publicado en FRED; no requiere token.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="b">
+        <v>1</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Elote</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>world_bank_maize</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>world_bank</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Maize</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>diagnostico_only</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>mensual</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>$/mt</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Proxy macro de maiz; no equivale directamente a elote fresco.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="b">
+        <v>1</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Plátano</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>world_bank_banana_us</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>world_bank</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Banana, US</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>diagnostico_only</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>mensual</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>$/kg</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Precio internacional de banana como contexto; validar antes de usar operacionalmente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="b">
+        <v>1</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Limón</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>world_bank_orange</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>world_bank</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>debil</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>diagnostico_only</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>mensual</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>$/kg</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Proxy citrico debil; mantener como diagnostico salvo evidencia de backtesting.</t>
+        </is>
       </c>
     </row>
   </sheetData>
